--- a/herschel_raw_data_template.xlsx
+++ b/herschel_raw_data_template.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Zalora Sub Cat Type</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Zalora Color Family</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
@@ -730,7 +730,11 @@
           <t>Image URLs specific to this one variant only, separated by ' ; '. Used for Shopee/Lazada/TikTok — Zalora uses its own separate image field below.</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>If copying from a spec sheet showing both units (e.g. '1.10 lb / 0.5'), paste it as-is — the tool automatically takes the number AFTER the '/' as the kg value. A plain number with no slash also works fine.</t>
+        </is>
+      </c>
       <c r="S2" s="2" t="inlineStr"/>
       <c r="T2" s="2" t="inlineStr"/>
       <c r="U2" s="2" t="inlineStr"/>
@@ -751,7 +755,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>Free text, one point per line (paste your full bullet list here if you like) — the tool automatically picks out the first recognizable material keyword (e.g. Polyester, Leather, Nylon) to use in Shopee/Lazada/Zalora's Material fields.</t>
+          <t>Free text, one point per line (paste your full bullet list here if you like) — the tool automatically picks out the first recognizable material keyword (e.g. Polyester, Leather, Nylon) to use in Shopee/Lazada/TikTok/Zalora's Material fields.</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -771,12 +775,24 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>'Key=Value' pairs separated by ' ; '. Written to generic Specification columns — TikTok's real template needs these under specific attribute-ID columns per category, so copy them over manually before uploading.</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr"/>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
+          <t>'Key=Value' pairs separated by ' ; '. A key matching one of TikTok's named columns (Jenis Kulit, Pola, Acara, Gaya, Instruksi Mencuci, Tipe Pengencang, Tipe Tas, Fitur, Bahan) lands directly in that column — e.g. 'Pola=Solid' fills the Pola column. Unmatched keys are dropped.</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>For Zalora's Season column.</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>For Zalora's Year column.</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>This also drives automatic ColorFamily classification — the tool looks at the first Zalora Image's dominant color first, falling back to matching keywords in this Color name if no image is available.</t>
+        </is>
+      </c>
       <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>Zalora's own image set (different dimensions than the other 3 marketplaces), separated by ' ; '.</t>
@@ -852,8 +868,10 @@
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="n">
-        <v>0.8</v>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>1.10 lb / 0.5</t>
+        </is>
       </c>
       <c r="S3" s="3" t="n">
         <v>48</v>
@@ -902,22 +920,20 @@
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>Capacity=25L</t>
+          <t>Pola=Solid</t>
         </is>
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>Backpacks</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
+          <t>Autumn-Winter</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>2026</v>
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Pink Sheep</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr">

--- a/herschel_raw_data_template.xlsx
+++ b/herschel_raw_data_template.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -482,7 +482,6 @@
     <col width="26" customWidth="1" min="30" max="30"/>
     <col width="26" customWidth="1" min="31" max="31"/>
     <col width="26" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -558,95 +557,90 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Stock / Quantity</t>
+          <t>Parent Images</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Parent Images</t>
+          <t>Variant Images (optional)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Variant Images (optional)</t>
+          <t>Weight (kg)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Weight (kg)</t>
+          <t>Length (cm)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Length (cm)</t>
+          <t>Width (cm)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Width (cm)</t>
+          <t>Height (cm)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Height (cm)</t>
+          <t>Product Type</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Product Type</t>
+          <t>Specific Category</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Specific Category</t>
+          <t>Gender*</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Gender*</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Shopee Shipping Service</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Shopee Shipping Service</t>
+          <t>Shopee Item Specifications</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Shopee Item Specifications</t>
+          <t>Lazada Item Specifications</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Lazada Item Specifications</t>
+          <t>TikTok Item Specifications</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>TikTok Item Specifications</t>
+          <t>Season</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Season</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Zalora Color</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Zalora Color</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Zalora Images</t>
         </is>
@@ -719,81 +713,80 @@
           <t>Selling price, numbers only.</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Image URLs shared by all variants, separated by ' ; ' (space-semicolon-space). Used for Shopee/Lazada/TikTok.</t>
+        </is>
+      </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Image URLs shared by all variants, separated by ' ; ' (space-semicolon-space). Used for Shopee/Lazada/TikTok.</t>
+          <t>Image URLs specific to this one variant only, separated by ' ; '. Used for Shopee/Lazada/TikTok — Zalora uses its own separate image field below.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Image URLs specific to this one variant only, separated by ' ; '. Used for Shopee/Lazada/TikTok — Zalora uses its own separate image field below.</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
           <t>If copying from a spec sheet showing both units (e.g. '1.10 lb / 0.5'), paste it as-is — the tool automatically takes the number AFTER the '/' as the kg value. A plain number with no slash also works fine.</t>
         </is>
       </c>
+      <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr"/>
       <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>e.g. BAGS or ACCESSORY. Used with Specific Category and Gender for an EXACT match against your Category Mapping file — not a keyword search.</t>
+        </is>
+      </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>e.g. BAGS or ACCESSORY. Used with Specific Category and Gender for an EXACT match against your Category Mapping file — not a keyword search.</t>
+          <t>e.g. BACKPACKS, TOTES, MESSENGER, DUFFLES, WAIST BAGS, LUNCH BOX, ORGANIZER.</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>e.g. BACKPACKS, TOTES, MESSENGER, DUFFLES, WAIST BAGS, LUNCH BOX, ORGANIZER.</t>
+          <t>Code: US, WN, or UK. Also translated into Zalora's own Gender field (US=Men, WN=Women, UK=Kids).</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>Code: US, WN, or UK. Also translated into Zalora's own Gender field (US=Men, WN=Women, UK=Kids).</t>
+          <t>Free text, one point per line (paste your full bullet list here if you like) — the tool automatically picks out the first recognizable material keyword (e.g. Polyester, Leather, Nylon) to use in Shopee/Lazada/TikTok/Zalora's Material fields.</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>Free text, one point per line (paste your full bullet list here if you like) — the tool automatically picks out the first recognizable material keyword (e.g. Polyester, Leather, Nylon) to use in Shopee/Lazada/TikTok/Zalora's Material fields.</t>
+          <t>Pasted as-is into Shopee's Shipping Service Details column.</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>Pasted as-is into Shopee's Shipping Service Details column.</t>
+          <t>'Key=Value' pairs separated by ' ; ', appended AFTER the automatic Brand=Herschel and Material=... entries.</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>'Key=Value' pairs separated by ' ; ', appended AFTER the automatic Brand=Herschel and Material=... entries.</t>
+          <t>'Key=Value' pairs separated by ' ; ', appended AFTER the automatic delivery/Hazmat/material entries. Also feeds Lazada's Short Description bullets if that field is left blank.</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>'Key=Value' pairs separated by ' ; ', appended AFTER the automatic delivery/Hazmat/material entries. Also feeds Lazada's Short Description bullets if that field is left blank.</t>
+          <t>'Key=Value' pairs separated by ' ; '. A key matching one of TikTok's named columns (Jenis Kulit, Pola, Acara, Gaya, Instruksi Mencuci, Tipe Pengencang, Tipe Tas, Fitur, Bahan) lands directly in that column — e.g. 'Pola=Solid' fills the Pola column. Unmatched keys are dropped.</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>'Key=Value' pairs separated by ' ; '. A key matching one of TikTok's named columns (Jenis Kulit, Pola, Acara, Gaya, Instruksi Mencuci, Tipe Pengencang, Tipe Tas, Fitur, Bahan) lands directly in that column — e.g. 'Pola=Solid' fills the Pola column. Unmatched keys are dropped.</t>
+          <t>For Zalora's Season column.</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>For Zalora's Season column.</t>
+          <t>For Zalora's Year column.</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>For Zalora's Year column.</t>
+          <t>This also drives automatic ColorFamily classification — the tool looks at the first Zalora Image's dominant color first, falling back to matching keywords in this Color name if no image is available.</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
-        <is>
-          <t>This also drives automatic ColorFamily classification — the tool looks at the first Zalora Image's dominant color first, falling back to matching keywords in this Color name if no image is available.</t>
-        </is>
-      </c>
-      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>Zalora's own image set (different dimensions than the other 3 marketplaces), separated by ' ; '.</t>
         </is>
@@ -859,53 +852,55 @@
       <c r="N3" s="3" t="n">
         <v>1299000</v>
       </c>
-      <c r="O3" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>https://example.com/img1.jpg ; https://example.com/img2.jpg</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>1.10 lb / 0.5</t>
         </is>
       </c>
+      <c r="R3" s="3" t="n">
+        <v>48</v>
+      </c>
       <c r="S3" s="3" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="U3" s="3" t="n">
         <v>20</v>
       </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>BAGS</t>
+        </is>
+      </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>BAGS</t>
+          <t>BACKPACKS</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>BACKPACKS</t>
+          <t>US</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>Custom print inspired by the worlds of Minecraft
 100% recycled 600D polyester, excluding trims</t>
         </is>
       </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>Reguler (Cashless):18000.00, Instant:18000.00</t>
+        </is>
+      </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>Reguler (Cashless):18000.00, Instant:18000.00</t>
+          <t>Capacity=25L</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
@@ -915,28 +910,23 @@
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>Capacity=25L</t>
+          <t>Pola=Solid</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>Pola=Solid</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
           <t>Autumn-Winter</t>
         </is>
       </c>
-      <c r="AE3" s="3" t="n">
+      <c r="AD3" s="3" t="n">
         <v>2026</v>
       </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Pink Sheep</t>
+        </is>
+      </c>
       <c r="AF3" s="3" t="inlineStr">
-        <is>
-          <t>Pink Sheep</t>
-        </is>
-      </c>
-      <c r="AG3" s="3" t="inlineStr">
         <is>
           <t>https://example.com/zalora1.jpg ; https://example.com/zalora2.jpg</t>
         </is>
